--- a/daily-routine-90-days.xlsx
+++ b/daily-routine-90-days.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adityasandhu/Desktop/repositories_github/crypto-asaqx645/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD30AA3B-1DF7-F246-A17B-F6431BEE6DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B899E2-6B9B-7440-B383-A274378DF3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="740" yWindow="500" windowWidth="28060" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
     <t>Week 1</t>
   </si>
   <si>
-    <t>Apr 9, 2026 - Apr 10, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>Apr 9, 2026 - Apr 10, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Habit</t>
@@ -85,7 +85,7 @@
     <t>Week 2</t>
   </si>
   <si>
-    <t>Apr 13, 2026 - Apr 17, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>Apr 13, 2026 - Apr 17, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -111,7 +111,7 @@
     <t>Week 3</t>
   </si>
   <si>
-    <t>Apr 20, 2026 - Apr 24, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>Apr 20, 2026 - Apr 24, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -137,7 +137,7 @@
     <t>Week 4</t>
   </si>
   <si>
-    <t>Apr 27, 2026 - May 1, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>Apr 27, 2026 - May 1, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -163,7 +163,7 @@
     <t>Week 5</t>
   </si>
   <si>
-    <t>May 4, 2026 - May 8, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>May 4, 2026 - May 8, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -189,7 +189,7 @@
     <t>Week 6</t>
   </si>
   <si>
-    <t>May 11, 2026 - May 15, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>May 11, 2026 - May 15, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -215,7 +215,7 @@
     <t>Week 7</t>
   </si>
   <si>
-    <t>May 18, 2026 - May 22, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>May 18, 2026 - May 22, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -241,7 +241,7 @@
     <t>Week 8</t>
   </si>
   <si>
-    <t>May 25, 2026 - May 29, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>May 25, 2026 - May 29, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -267,7 +267,7 @@
     <t>Week 9</t>
   </si>
   <si>
-    <t>Jun 1, 2026 - Jun 5, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>Jun 1, 2026 - Jun 5, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -293,7 +293,7 @@
     <t>Week 10</t>
   </si>
   <si>
-    <t>Jun 8, 2026 - Jun 12, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>Jun 8, 2026 - Jun 12, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -319,7 +319,7 @@
     <t>Week 11</t>
   </si>
   <si>
-    <t>Jun 15, 2026 - Jun 19, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>Jun 15, 2026 - Jun 19, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -345,7 +345,7 @@
     <t>Week 12</t>
   </si>
   <si>
-    <t>Jun 22, 2026 - Jun 26, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>Jun 22, 2026 - Jun 26, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -371,7 +371,7 @@
     <t>Week 13</t>
   </si>
   <si>
-    <t>Jun 29, 2026 - Jul 3, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>Jun 29, 2026 - Jul 3, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -397,7 +397,7 @@
     <t>Week 14</t>
   </si>
   <si>
-    <t>Jul 6, 2026 - Jul 7, 2026 | Monday through Friday plan | Saturdays removed</t>
+    <t>Jul 6, 2026 - Jul 7, 2026 | Monday through Friday plan</t>
   </si>
   <si>
     <t>Mon
@@ -908,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="7" t="b">
         <v>0</v>
@@ -919,7 +919,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="7" t="b">
         <v>0</v>
@@ -930,7 +930,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="7" t="b">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="7" t="b">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="7" t="b">
         <v>0</v>
@@ -974,7 +974,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="7" t="b">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="7" t="b">
         <v>0</v>

--- a/daily-routine-90-days.xlsx
+++ b/daily-routine-90-days.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adityasandhu/Desktop/repositories_github/crypto-asaqx645/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B899E2-6B9B-7440-B383-A274378DF3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C53BC26-007B-B048-B061-148625587F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="740" yWindow="500" windowWidth="28060" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="111">
   <si>
     <t>Week 1</t>
   </si>
@@ -48,10 +48,6 @@
 Apr 9</t>
   </si>
   <si>
-    <t>Fri
-Apr 10</t>
-  </si>
-  <si>
     <t>4:00 a.m. Wake &amp; hydrate</t>
   </si>
   <si>
@@ -130,10 +126,6 @@
 Apr 23</t>
   </si>
   <si>
-    <t>Fri
-Apr 24</t>
-  </si>
-  <si>
     <t>Week 4</t>
   </si>
   <si>
@@ -406,13 +398,51 @@
   <si>
     <t>Tue
 Jul 7</t>
+  </si>
+  <si>
+    <t>Wake &amp; hydrate</t>
+  </si>
+  <si>
+    <t>2 km walk</t>
+  </si>
+  <si>
+    <t>Fri (off)
+Apr 24</t>
+  </si>
+  <si>
+    <t>Sat (off)
+Apr 25</t>
+  </si>
+  <si>
+    <t>Sun(off)
+Apr 26</t>
+  </si>
+  <si>
+    <t>Sat
+May 9</t>
+  </si>
+  <si>
+    <t>Sun
+May 10</t>
+  </si>
+  <si>
+    <t>Fri 
+Apr 10</t>
+  </si>
+  <si>
+    <t>Sat 
+Apr 11</t>
+  </si>
+  <si>
+    <t>Sun
+Apr 12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,6 +477,12 @@
       <color rgb="FF1D4ED8"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -871,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -899,118 +935,223 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="5" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C21" t="b">
+    <row r="17" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1020,6 +1161,7 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A15:C15"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1035,7 +1177,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1045,7 +1187,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1058,24 +1200,24 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -1095,7 +1237,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -1115,7 +1257,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -1135,7 +1277,7 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -1155,7 +1297,7 @@
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -1175,7 +1317,7 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -1195,7 +1337,7 @@
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -1215,7 +1357,7 @@
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -1235,7 +1377,7 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -1255,7 +1397,7 @@
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1284,7 +1426,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1294,7 +1436,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1307,24 +1449,24 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -1344,7 +1486,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -1364,7 +1506,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -1384,7 +1526,7 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -1404,7 +1546,7 @@
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -1424,7 +1566,7 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -1444,7 +1586,7 @@
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -1464,7 +1606,7 @@
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -1484,7 +1626,7 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -1504,7 +1646,7 @@
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1533,7 +1675,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1543,7 +1685,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1556,24 +1698,24 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -1593,7 +1735,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -1613,7 +1755,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -1633,7 +1775,7 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -1653,7 +1795,7 @@
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -1673,7 +1815,7 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -1693,7 +1835,7 @@
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -1713,7 +1855,7 @@
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -1733,7 +1875,7 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -1753,7 +1895,7 @@
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1782,7 +1924,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1792,7 +1934,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1805,24 +1947,24 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -1842,7 +1984,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -1862,7 +2004,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -1882,7 +2024,7 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -1902,7 +2044,7 @@
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -1922,7 +2064,7 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -1942,7 +2084,7 @@
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -1962,7 +2104,7 @@
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -1982,7 +2124,7 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -2002,7 +2144,7 @@
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2031,14 +2173,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
@@ -2048,15 +2190,15 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -2067,7 +2209,7 @@
     </row>
     <row r="6" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -2078,7 +2220,7 @@
     </row>
     <row r="7" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -2089,7 +2231,7 @@
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -2100,7 +2242,7 @@
     </row>
     <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -2111,7 +2253,7 @@
     </row>
     <row r="10" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -2122,7 +2264,7 @@
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -2133,7 +2275,7 @@
     </row>
     <row r="12" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -2144,7 +2286,7 @@
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -2155,7 +2297,7 @@
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
@@ -2181,7 +2323,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2191,7 +2333,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2204,24 +2346,24 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -2241,7 +2383,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -2261,7 +2403,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -2281,7 +2423,7 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -2301,7 +2443,7 @@
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -2321,7 +2463,7 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -2341,7 +2483,7 @@
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -2361,7 +2503,7 @@
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -2381,7 +2523,7 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -2401,7 +2543,7 @@
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2421,7 +2563,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -2430,7 +2572,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2440,7 +2582,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2453,24 +2595,21 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -2482,15 +2621,12 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -2502,15 +2638,12 @@
         <v>0</v>
       </c>
       <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -2522,15 +2655,12 @@
         <v>0</v>
       </c>
       <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -2542,15 +2672,12 @@
         <v>0</v>
       </c>
       <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -2562,15 +2689,12 @@
         <v>0</v>
       </c>
       <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -2582,15 +2706,12 @@
         <v>0</v>
       </c>
       <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -2602,15 +2723,12 @@
         <v>0</v>
       </c>
       <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -2622,15 +2740,12 @@
         <v>0</v>
       </c>
       <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -2642,21 +2757,158 @@
         <v>0</v>
       </c>
       <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2664,6 +2916,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2679,7 +2932,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2689,7 +2942,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2702,24 +2955,24 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -2739,7 +2992,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -2759,7 +3012,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -2779,7 +3032,7 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -2799,7 +3052,7 @@
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -2819,7 +3072,7 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -2839,7 +3092,7 @@
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -2859,7 +3112,7 @@
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -2879,7 +3132,7 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -2899,7 +3152,7 @@
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2919,7 +3172,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -2928,7 +3181,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2938,7 +3191,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2951,24 +3204,21 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -2980,15 +3230,12 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -3000,15 +3247,12 @@
         <v>0</v>
       </c>
       <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -3020,15 +3264,12 @@
         <v>0</v>
       </c>
       <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -3040,15 +3281,12 @@
         <v>0</v>
       </c>
       <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -3060,15 +3298,12 @@
         <v>0</v>
       </c>
       <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -3080,15 +3315,12 @@
         <v>0</v>
       </c>
       <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -3100,15 +3332,12 @@
         <v>0</v>
       </c>
       <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -3120,15 +3349,12 @@
         <v>0</v>
       </c>
       <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -3140,21 +3366,158 @@
         <v>0</v>
       </c>
       <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3162,6 +3525,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3177,7 +3541,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3187,7 +3551,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3200,24 +3564,24 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -3237,7 +3601,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -3257,7 +3621,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -3277,7 +3641,7 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -3297,7 +3661,7 @@
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -3317,7 +3681,7 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -3337,7 +3701,7 @@
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -3357,7 +3721,7 @@
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -3377,7 +3741,7 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -3397,7 +3761,7 @@
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -3426,7 +3790,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3436,7 +3800,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3449,24 +3813,24 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -3486,7 +3850,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -3506,7 +3870,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -3526,7 +3890,7 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -3546,7 +3910,7 @@
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -3566,7 +3930,7 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -3586,7 +3950,7 @@
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -3606,7 +3970,7 @@
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -3626,7 +3990,7 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -3646,7 +4010,7 @@
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -3675,7 +4039,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3685,7 +4049,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3698,24 +4062,24 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -3735,7 +4099,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -3755,7 +4119,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -3775,7 +4139,7 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -3795,7 +4159,7 @@
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -3815,7 +4179,7 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -3835,7 +4199,7 @@
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -3855,7 +4219,7 @@
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -3875,7 +4239,7 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -3895,7 +4259,7 @@
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -3924,7 +4288,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3934,7 +4298,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3947,24 +4311,24 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="b">
         <v>0</v>
@@ -3984,7 +4348,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>0</v>
@@ -4004,7 +4368,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>0</v>
@@ -4024,7 +4388,7 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="b">
         <v>0</v>
@@ -4044,7 +4408,7 @@
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="b">
         <v>0</v>
@@ -4064,7 +4428,7 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="b">
         <v>0</v>
@@ -4084,7 +4448,7 @@
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7" t="b">
         <v>0</v>
@@ -4104,7 +4468,7 @@
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7" t="b">
         <v>0</v>
@@ -4124,7 +4488,7 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="b">
         <v>0</v>
@@ -4144,7 +4508,7 @@
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>

--- a/daily-routine-90-days.xlsx
+++ b/daily-routine-90-days.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adityasandhu/Desktop/repositories_github/crypto-asaqx645/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C53BC26-007B-B048-B061-148625587F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C83E2A1-4702-9B4B-ACFA-935A807475D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="740" yWindow="500" windowWidth="28060" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1048,7 +1048,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" s="7" t="b">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>102</v>
       </c>
       <c r="B21" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="7" t="b">
         <v>0</v>
@@ -1090,7 +1090,7 @@
         <v>10</v>
       </c>
       <c r="B22" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="7" t="b">
         <v>0</v>
@@ -1104,7 +1104,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="7" t="b">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" s="7" t="b">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="7" t="b">
         <v>0</v>

--- a/daily-routine-90-days.xlsx
+++ b/daily-routine-90-days.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adityasandhu/Desktop/repositories_github/crypto-asaqx645/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C83E2A1-4702-9B4B-ACFA-935A807475D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B140F847-429C-9F4D-AB13-D8C726B90ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="740" yWindow="500" windowWidth="28060" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="112">
   <si>
     <t>Week 1</t>
   </si>
@@ -436,6 +436,9 @@
   <si>
     <t>Sun
 Apr 12</t>
+  </si>
+  <si>
+    <t>Day 1-4</t>
   </si>
 </sst>
 </file>
@@ -564,13 +567,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -580,14 +591,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,18 +919,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="5"/>
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -935,12 +939,15 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4" s="8" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
+      <c r="B5" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -948,7 +955,7 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
+      <c r="B6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -956,7 +963,7 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
+      <c r="B7" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -964,7 +971,7 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
+      <c r="B8" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -972,7 +979,7 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
+      <c r="B9" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -980,7 +987,7 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
+      <c r="B10" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -988,7 +995,7 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
+      <c r="B11" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -996,7 +1003,7 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
+      <c r="B12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1004,16 +1011,16 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
+      <c r="B13" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="17" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -1033,13 +1040,13 @@
       <c r="A18" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="7" t="b">
+      <c r="B18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="C18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7" t="b">
+      <c r="C18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1047,13 +1054,13 @@
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="7" t="b">
+      <c r="B19" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="C19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7" t="b">
+      <c r="C19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1061,13 +1068,13 @@
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="7" t="b">
+      <c r="B20" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="C20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7" t="b">
+      <c r="C20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1075,13 +1082,13 @@
       <c r="A21" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="7" t="b">
+      <c r="B21" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="C21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7" t="b">
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1089,13 +1096,13 @@
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="7" t="b">
+      <c r="B22" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="C22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7" t="b">
+      <c r="C22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1103,13 +1110,13 @@
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="7" t="b">
+      <c r="B23" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="C23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7" t="b">
+      <c r="C23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1117,13 +1124,13 @@
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="7" t="b">
+      <c r="B24" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="C24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7" t="b">
+      <c r="C24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1131,13 +1138,13 @@
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="7" t="b">
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1145,13 +1152,13 @@
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="7" t="b">
+      <c r="B26" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="C26" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7" t="b">
+      <c r="C26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1176,24 +1183,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1219,19 +1226,19 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1239,19 +1246,19 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1259,19 +1266,19 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1279,19 +1286,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1299,19 +1306,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1319,19 +1326,19 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1339,19 +1346,19 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1359,19 +1366,19 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1379,31 +1386,31 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1425,24 +1432,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1468,19 +1475,19 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1488,19 +1495,19 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1508,19 +1515,19 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1528,19 +1535,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1548,19 +1555,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1568,19 +1575,19 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1588,19 +1595,19 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1608,19 +1615,19 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1628,31 +1635,31 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1674,24 +1681,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1717,19 +1724,19 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1737,19 +1744,19 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1757,19 +1764,19 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1777,19 +1784,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1797,19 +1804,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1817,19 +1824,19 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1837,19 +1844,19 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1857,19 +1864,19 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1877,31 +1884,31 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1923,24 +1930,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1966,19 +1973,19 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1986,19 +1993,19 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2006,19 +2013,19 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2026,19 +2033,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2046,19 +2053,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2066,19 +2073,19 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2086,19 +2093,19 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2106,19 +2113,19 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2126,31 +2133,31 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2172,18 +2179,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2200,10 +2207,10 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2211,10 +2218,10 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2222,10 +2229,10 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2233,10 +2240,10 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2244,10 +2251,10 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2255,10 +2262,10 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2266,10 +2273,10 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2277,10 +2284,10 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2288,19 +2295,19 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2322,24 +2329,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2365,19 +2372,19 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2385,19 +2392,19 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2405,19 +2412,19 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2425,19 +2432,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2445,19 +2452,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2465,19 +2472,19 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2485,19 +2492,19 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2505,19 +2512,19 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2525,31 +2532,31 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2571,24 +2578,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2611,16 +2618,16 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2628,16 +2635,16 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2645,16 +2652,16 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2662,16 +2669,16 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2679,16 +2686,16 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2696,16 +2703,16 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2713,16 +2720,16 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2730,16 +2737,16 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2747,28 +2754,28 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -2788,13 +2795,13 @@
       <c r="A17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7" t="b">
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2802,13 +2809,13 @@
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7" t="b">
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2816,13 +2823,13 @@
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7" t="b">
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2830,13 +2837,13 @@
       <c r="A20" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7" t="b">
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2844,13 +2851,13 @@
       <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7" t="b">
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2858,13 +2865,13 @@
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7" t="b">
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2872,13 +2879,13 @@
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7" t="b">
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2886,13 +2893,13 @@
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7" t="b">
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2900,13 +2907,13 @@
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="7" t="b">
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2931,24 +2938,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2974,19 +2981,19 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2994,19 +3001,19 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3014,19 +3021,19 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3034,19 +3041,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3054,19 +3061,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3074,19 +3081,19 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3094,19 +3101,19 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3114,19 +3121,19 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3134,31 +3141,31 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3180,24 +3187,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3220,16 +3227,16 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3237,16 +3244,16 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3254,16 +3261,16 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3271,16 +3278,16 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3288,16 +3295,16 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3305,16 +3312,16 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3322,16 +3329,16 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3339,16 +3346,16 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3356,28 +3363,28 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -3397,13 +3404,13 @@
       <c r="A17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7" t="b">
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3411,13 +3418,13 @@
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7" t="b">
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3425,13 +3432,13 @@
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7" t="b">
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3439,13 +3446,13 @@
       <c r="A20" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7" t="b">
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3453,13 +3460,13 @@
       <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7" t="b">
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3467,13 +3474,13 @@
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7" t="b">
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3481,13 +3488,13 @@
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7" t="b">
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3495,13 +3502,13 @@
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7" t="b">
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3509,13 +3516,13 @@
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="7" t="b">
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3540,24 +3547,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3583,19 +3590,19 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3603,19 +3610,19 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3623,19 +3630,19 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3643,19 +3650,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3663,19 +3670,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3683,19 +3690,19 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3703,19 +3710,19 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3723,19 +3730,19 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3743,31 +3750,31 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3789,24 +3796,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3832,19 +3839,19 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3852,19 +3859,19 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3872,19 +3879,19 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3892,19 +3899,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3912,19 +3919,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3932,19 +3939,19 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3952,19 +3959,19 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3972,19 +3979,19 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3992,31 +3999,31 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4038,24 +4045,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -4081,19 +4088,19 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4101,19 +4108,19 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4121,19 +4128,19 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4141,19 +4148,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4161,19 +4168,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4181,19 +4188,19 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4201,19 +4208,19 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4221,19 +4228,19 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4241,31 +4248,31 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4287,24 +4294,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -4330,19 +4337,19 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="b">
+      <c r="B5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4350,19 +4357,19 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
+      <c r="B6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4370,19 +4377,19 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="b">
+      <c r="B7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4390,19 +4397,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="b">
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4410,19 +4417,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="b">
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4430,19 +4437,19 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="b">
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4450,19 +4457,19 @@
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="b">
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4470,19 +4477,19 @@
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="b">
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4490,31 +4497,31 @@
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="b">
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/daily-routine-90-days.xlsx
+++ b/daily-routine-90-days.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adityasandhu/Desktop/repositories_github/crypto-asaqx645/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B140F847-429C-9F4D-AB13-D8C726B90ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2AA8F9-A521-1746-B7F8-D7D46A23CDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="740" yWindow="500" windowWidth="28060" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="740" yWindow="500" windowWidth="28060" windowHeight="17500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="112">
   <si>
     <t>Week 1</t>
   </si>
@@ -1047,7 +1047,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -1061,7 +1061,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -1103,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -1117,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -1131,7 +1131,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -1145,7 +1145,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -1159,7 +1159,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2570,7 +2570,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -2877,7 +2877,7 @@
     </row>
     <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23" s="3" t="b">
         <v>0</v>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B24" s="3" t="b">
         <v>0</v>
@@ -2900,20 +2900,6 @@
         <v>0</v>
       </c>
       <c r="D24" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
     </row>
